--- a/mlai-internship/train_test_split_demo.xlsx
+++ b/mlai-internship/train_test_split_demo.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10118"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://opsracsch-my.sharepoint.com/personal/k41929_365oft_top/Documents/aiml-tranining/aiml/mlai-internship/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="26" documentId="8_{6DBDEEE6-2B21-2043-808F-B6A0FFE2B822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F72732F5-1DB3-424E-B4E1-82641EF820F8}"/>
+  <xr:revisionPtr revIDLastSave="39" documentId="8_{6DBDEEE6-2B21-2043-808F-B6A0FFE2B822}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C095054A-AE35-C645-A0A7-14375F2E6C1B}"/>
   <bookViews>
-    <workbookView xWindow="-25600" yWindow="600" windowWidth="25600" windowHeight="19880" xr2:uid="{F176BB25-F591-8F4B-9A40-8DCF46369232}"/>
+    <workbookView xWindow="29380" yWindow="600" windowWidth="20480" windowHeight="14760" xr2:uid="{F176BB25-F591-8F4B-9A40-8DCF46369232}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="35" uniqueCount="35">
   <si>
     <t>F1</t>
   </si>
@@ -120,13 +120,34 @@
   </si>
   <si>
     <t>y_test (4x1)</t>
+  </si>
+  <si>
+    <t>150x5</t>
+  </si>
+  <si>
+    <t>150x4</t>
+  </si>
+  <si>
+    <t>150x1</t>
+  </si>
+  <si>
+    <t>120x4</t>
+  </si>
+  <si>
+    <t>30x4</t>
+  </si>
+  <si>
+    <t>120x1</t>
+  </si>
+  <si>
+    <t>30x1</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -161,6 +182,13 @@
       <name val="Aptos Narrow"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="20"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -332,7 +360,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -361,7 +389,7 @@
     <xf numFmtId="0" fontId="4" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -385,6 +413,7 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -719,13 +748,14 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBD6AFCB-4CD1-744E-8B8F-C1423CD89EFC}">
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
+    <col min="6" max="6" width="13" customWidth="1"/>
     <col min="8" max="8" width="17.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" ht="19" x14ac:dyDescent="0.2">
       <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
@@ -742,7 +772,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:9" ht="22" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" ht="22" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -763,7 +793,7 @@
       </c>
       <c r="I2" s="5"/>
     </row>
-    <row r="3" spans="1:9" ht="22" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -779,8 +809,11 @@
       <c r="I3" s="5" t="s">
         <v>16</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="J3" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -796,8 +829,11 @@
       <c r="I4" s="5" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="J4" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -813,8 +849,11 @@
       <c r="I5" s="5" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="22" x14ac:dyDescent="0.3">
+      <c r="J5" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" ht="22" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -830,8 +869,11 @@
       <c r="I6" s="5" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="J6" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7">
         <v>6</v>
       </c>
@@ -842,7 +884,7 @@
       <c r="F7" s="18"/>
       <c r="G7" s="7"/>
     </row>
-    <row r="8" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8">
         <v>7</v>
       </c>
@@ -853,7 +895,7 @@
       <c r="F8" s="18"/>
       <c r="G8" s="7"/>
     </row>
-    <row r="9" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9">
         <v>8</v>
       </c>
@@ -864,7 +906,7 @@
       <c r="F9" s="18"/>
       <c r="G9" s="7"/>
     </row>
-    <row r="10" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10">
         <v>9</v>
       </c>
@@ -875,7 +917,7 @@
       <c r="F10" s="18"/>
       <c r="G10" s="7"/>
     </row>
-    <row r="11" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11">
         <v>10</v>
       </c>
@@ -886,7 +928,7 @@
       <c r="F11" s="18"/>
       <c r="G11" s="7"/>
     </row>
-    <row r="12" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12">
         <v>11</v>
       </c>
@@ -897,7 +939,7 @@
       <c r="F12" s="18"/>
       <c r="G12" s="7"/>
     </row>
-    <row r="13" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13">
         <v>12</v>
       </c>
@@ -908,7 +950,7 @@
       <c r="F13" s="18"/>
       <c r="G13" s="7"/>
     </row>
-    <row r="14" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14">
         <v>13</v>
       </c>
@@ -919,7 +961,7 @@
       <c r="F14" s="18"/>
       <c r="G14" s="7"/>
     </row>
-    <row r="15" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15">
         <v>14</v>
       </c>
@@ -930,7 +972,7 @@
       <c r="F15" s="18"/>
       <c r="G15" s="7"/>
     </row>
-    <row r="16" spans="1:9" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" ht="19" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1013,28 +1055,37 @@
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" ht="27" x14ac:dyDescent="0.35">
       <c r="B24" s="1" t="s">
         <v>6</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="24" x14ac:dyDescent="0.3">
+      <c r="D24" s="20" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="27" x14ac:dyDescent="0.35">
       <c r="B25" s="1" t="s">
         <v>7</v>
       </c>
       <c r="C25" s="1" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="D25" s="20" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="27" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>9</v>
       </c>
       <c r="C26" t="s">
         <v>10</v>
+      </c>
+      <c r="D26" s="20" t="s">
+        <v>30</v>
       </c>
     </row>
   </sheetData>
